--- a/config/custFactorTemplate.xlsx
+++ b/config/custFactorTemplate.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="XxBduxdJB9q7JCa34WKyWuuR69xiYp9fs6QUCJsJh9OMdCixuLj8Hxj3ukxdjFOIEmlRm3iGc/sumhVZXS4P2w==" workbookSaltValue="Itd2T1UBaWWzXywK+Q7WzA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView windowWidth="24525" windowHeight="12165"/>
+    <workbookView windowWidth="25380" windowHeight="12165"/>
   </bookViews>
   <sheets>
     <sheet name="1、折算系数表" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF0A1E2C"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>PerfectMatch</t>
     </r>
     <r>
@@ -147,7 +154,7 @@
     <t>客户C</t>
   </si>
   <si>
-    <t>客户D</t>
+    <t>客户DD</t>
   </si>
   <si>
     <t>ErrorMessage</t>
